--- a/data/demo/volunteer_shifts.xlsx
+++ b/data/demo/volunteer_shifts.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Смены октябрь" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Регулярные занятия" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,33 +413,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>дата</t>
+          <t>день</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>программа</t>
+          <t>время</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>район</t>
+          <t>занятие</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>время</t>
+          <t>регион</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>нужно волонтёров</t>
+          <t>формат</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -451,26 +451,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>суббота</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Продукты к двери</t>
+          <t>12:00–14:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Северный</t>
+          <t>инклюзивная мастерская: керамика</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10:00–13:00</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>очно</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -481,120 +483,224 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>суббота</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Сопровождение</t>
+          <t>15:00–17:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Центральный</t>
+          <t>инклюзивная мастерская: живопись</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>09:00–12:00</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>очно</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Олег</t>
+          <t>Анна</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>суббота</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Тёплый звонок</t>
+          <t>12:00–14:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>онлайн</t>
+          <t>инклюзивная мастерская: валяние</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>18:00–20:00</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>6</v>
+          <t>Московская область</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>очно</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Мария</t>
+          <t>Ольга</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>вторник</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Мастер на час</t>
+          <t>10:00–12:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Южный</t>
+          <t>занятие с группой из интерната: керамика</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11:00–15:00</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>3</v>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>очно</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Олег</t>
+          <t>Михаил</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>четверг</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Продукты к двери</t>
+          <t>11:00–13:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Южный</t>
+          <t>занятие с группой из интерната: кулинария</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10:00–13:00</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>5</v>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>очно</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Анна</t>
+          <t>Михаил</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>среда</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>19:00–20:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>созвон наставников с психологом</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>все регионы</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>онлайн</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ирина</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>пятница</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>15:00–17:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>занятие с группой из интерната: живопись</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Ярославская область</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>очно</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Светлана</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>воскресенье</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>13:00–15:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>мастерская для выпускников</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Северная Осетия</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>очно</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Залина</t>
         </is>
       </c>
     </row>
